--- a/ch_03/ch_03_solution.xlsx
+++ b/ch_03/ch_03_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_03_data_viz_seaborn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4C660D-9FA4-46FB-BB80-5B5C5811AF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8600577D-2974-4E8D-854A-9E8B4B23EE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mpg" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -550,15 +550,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>59267</xdr:colOff>
+      <xdr:colOff>194815</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>177555</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>437034</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>84667</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>157528</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>79309</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -573,7 +573,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A10"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A11"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -586,8 +586,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="872067" y="1651000"/>
-          <a:ext cx="2155767" cy="1710267"/>
+          <a:off x="1000777" y="1793142"/>
+          <a:ext cx="2611396" cy="2055869"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -600,14 +600,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>639233</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6232</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -622,7 +622,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A22"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A24"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -648,15 +648,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>110067</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:colOff>110066</xdr:colOff>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>46567</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>185042</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>148168</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>936268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -671,7 +671,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A63"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A66"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -684,8 +684,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="753534" y="12606867"/>
-          <a:ext cx="2741975" cy="2103967"/>
+          <a:off x="916028" y="12421740"/>
+          <a:ext cx="3993009" cy="3043816"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -698,14 +698,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>440266</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>855506</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>114302</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -720,7 +720,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A79"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A82"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -747,14 +747,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>160866</xdr:rowOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>160865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>136339</xdr:rowOff>
+      <xdr:colOff>835270</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>137678</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -769,7 +769,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A99"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A102"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -782,8 +782,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1206500" y="29468233"/>
-          <a:ext cx="3289300" cy="2523939"/>
+          <a:off x="1199662" y="19606519"/>
+          <a:ext cx="3973146" cy="3028477"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -796,14 +796,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>537634</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>876389</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>50424</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>791308</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -818,7 +818,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A117"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A120"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -831,8 +831,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="537634" y="33972500"/>
-          <a:ext cx="2929555" cy="2247900"/>
+          <a:off x="537634" y="22868060"/>
+          <a:ext cx="3850328" cy="2933700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -845,14 +845,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>622301</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>694267</xdr:colOff>
-      <xdr:row>173</xdr:row>
-      <xdr:rowOff>93134</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>1310598</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -867,7 +867,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A155"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A158"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -880,8 +880,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="622301" y="36588701"/>
-          <a:ext cx="3551766" cy="3551766"/>
+          <a:off x="622301" y="34575750"/>
+          <a:ext cx="4751997" cy="4721281"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -894,14 +894,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>596901</xdr:colOff>
-      <xdr:row>175</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>165101</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>613187</xdr:colOff>
-      <xdr:row>193</xdr:row>
-      <xdr:rowOff>42335</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>702312</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>1883019</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -916,7 +916,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A177"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A180"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -929,8 +929,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="596901" y="40576501"/>
-          <a:ext cx="3496086" cy="3153834"/>
+          <a:off x="596901" y="39789101"/>
+          <a:ext cx="5325844" cy="4769582"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -942,15 +942,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>110067</xdr:colOff>
-      <xdr:row>206</xdr:row>
+      <xdr:colOff>110066</xdr:colOff>
+      <xdr:row>209</xdr:row>
       <xdr:rowOff>84667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>523608</xdr:colOff>
-      <xdr:row>220</xdr:row>
-      <xdr:rowOff>67734</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>454268</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>1630121</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -965,7 +965,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A207"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A210"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -978,8 +978,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="922867" y="46139100"/>
-          <a:ext cx="3080541" cy="2531534"/>
+          <a:off x="916028" y="47346985"/>
+          <a:ext cx="4758673" cy="3879078"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -992,14 +992,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>71967</xdr:colOff>
-      <xdr:row>222</xdr:row>
+      <xdr:row>225</xdr:row>
       <xdr:rowOff>29633</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>198967</xdr:colOff>
-      <xdr:row>234</xdr:row>
-      <xdr:rowOff>141292</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>1545878</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1014,7 +1014,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A223"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A226"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1027,8 +1027,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="884767" y="48996600"/>
-          <a:ext cx="2794000" cy="2296059"/>
+          <a:off x="877929" y="51750383"/>
+          <a:ext cx="4496369" cy="3670360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1041,14 +1041,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>239</xdr:row>
+      <xdr:row>242</xdr:row>
       <xdr:rowOff>80434</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>828443</xdr:colOff>
-      <xdr:row>250</xdr:row>
-      <xdr:rowOff>173567</xdr:rowOff>
+      <xdr:row>253</xdr:row>
+      <xdr:rowOff>173568</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1063,7 +1063,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A240"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A243"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1089,15 +1089,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>110067</xdr:colOff>
-      <xdr:row>254</xdr:row>
+      <xdr:colOff>110066</xdr:colOff>
+      <xdr:row>257</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>731985</xdr:colOff>
-      <xdr:row>264</xdr:row>
-      <xdr:rowOff>59267</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>413970</xdr:colOff>
+      <xdr:row>269</xdr:row>
+      <xdr:rowOff>176259</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1112,7 +1112,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A255"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A258"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1125,8 +1125,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="922867" y="54830133"/>
-          <a:ext cx="2399918" cy="1841500"/>
+          <a:off x="916028" y="59290927"/>
+          <a:ext cx="4718375" cy="3589140"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1139,13 +1139,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>347135</xdr:colOff>
-      <xdr:row>269</xdr:row>
+      <xdr:row>272</xdr:row>
       <xdr:rowOff>169335</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>503767</xdr:colOff>
-      <xdr:row>287</xdr:row>
+      <xdr:row>290</xdr:row>
       <xdr:rowOff>1428</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1161,7 +1161,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A270"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A273"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1188,13 +1188,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>270934</xdr:colOff>
-      <xdr:row>305</xdr:row>
+      <xdr:row>308</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>374582</xdr:colOff>
-      <xdr:row>319</xdr:row>
+      <xdr:row>322</xdr:row>
       <xdr:rowOff>103298</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1210,7 +1210,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A306"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A309"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1237,13 +1237,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>156634</xdr:colOff>
-      <xdr:row>342</xdr:row>
+      <xdr:row>345</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>699024</xdr:colOff>
-      <xdr:row>356</xdr:row>
+      <xdr:row>359</xdr:row>
       <xdr:rowOff>46566</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1259,7 +1259,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A343"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A346"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1291,9 +1291,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>156633</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>157420</xdr:rowOff>
+      <xdr:colOff>322385</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>102571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1321,8 +1321,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="855133" y="0"/>
-          <a:ext cx="1892300" cy="1431653"/>
+          <a:off x="848295" y="0"/>
+          <a:ext cx="2045840" cy="1538648"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1334,15 +1334,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>110067</xdr:rowOff>
+      <xdr:colOff>253999</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>110066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>784469</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>67733</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>465258</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>632993</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1357,7 +1357,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A36"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A38"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1370,8 +1370,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1066800" y="6299200"/>
-          <a:ext cx="4975469" cy="1960033"/>
+          <a:off x="1059961" y="6572412"/>
+          <a:ext cx="6391519" cy="2497533"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1384,14 +1384,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>211667</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>512164</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>110066</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>505265</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>69604</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1406,7 +1406,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A47"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A50"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1419,8 +1419,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1024467" y="8449733"/>
-          <a:ext cx="5634497" cy="1854200"/>
+          <a:off x="1017629" y="9579218"/>
+          <a:ext cx="7122290" cy="2327031"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1432,15 +1432,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>289</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>538529</xdr:colOff>
+      <xdr:row>292</xdr:row>
+      <xdr:rowOff>69606</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>16933</xdr:colOff>
-      <xdr:row>301</xdr:row>
-      <xdr:rowOff>78925</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>582491</xdr:colOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>554316</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1455,7 +1455,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A290"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A293"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1468,8 +1468,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="59888967"/>
-          <a:ext cx="3496733" cy="2263325"/>
+          <a:off x="538529" y="66902135"/>
+          <a:ext cx="4381500" cy="2818335"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1482,13 +1482,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>431032</xdr:colOff>
-      <xdr:row>323</xdr:row>
+      <xdr:row>326</xdr:row>
       <xdr:rowOff>23093</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>46182</xdr:colOff>
-      <xdr:row>340</xdr:row>
+      <xdr:row>343</xdr:row>
       <xdr:rowOff>102629</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1504,7 +1504,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A324"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A327"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1530,15 +1530,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:colOff>581024</xdr:colOff>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>484297</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>624384</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>948836</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1553,7 +1553,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A131"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A134"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1566,8 +1566,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="581025" y="23431500"/>
-          <a:ext cx="2470260" cy="1895475"/>
+          <a:off x="581024" y="26964543"/>
+          <a:ext cx="3498005" cy="2658207"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1579,15 +1579,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>766762</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:colOff>766761</xdr:colOff>
+      <xdr:row>144</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>707274</xdr:colOff>
-      <xdr:row>152</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>326048</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>1297688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1602,7 +1602,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A143"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A146"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1615,8 +1615,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="766762" y="25650825"/>
-          <a:ext cx="2507500" cy="1924050"/>
+          <a:off x="766761" y="30430177"/>
+          <a:ext cx="3896825" cy="2959434"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12422,7 +12422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE8A746-C358-490F-985F-C2AE3E23621E}">
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.265625" style="4" customWidth="1"/>
@@ -12435,338 +12435,349 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="e" cm="1" vm="3">
-        <f t="array" ref="A10">_xlfn._xlws.PY(2,0)</f>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="e" cm="1" vm="3">
+        <f t="array" ref="A11">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" s="4" t="e" cm="1" vm="4">
-        <f t="array" ref="A22">_xlfn._xlws.PY(3,0)</f>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" s="4" t="e" cm="1" vm="4">
+        <f t="array" ref="A24">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A36" s="4" t="e" cm="1" vm="5">
-        <f t="array" ref="A36">_xlfn._xlws.PY(4,0)</f>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" s="4" t="e" cm="1" vm="5">
+        <f t="array" ref="A38">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A47" s="4" t="e" cm="1" vm="6">
-        <f t="array" ref="A47">_xlfn._xlws.PY(5,0)</f>
+    <row r="48" spans="1:1" ht="69.849999999999994" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" s="4" t="e" cm="1" vm="6">
+        <f t="array" ref="A50">_xlfn._xlws.PY(5,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A63" s="4" t="e" cm="1" vm="7">
-        <f t="array" ref="A63">_xlfn._xlws.PY(6,0)</f>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" s="4" t="e" cm="1" vm="7">
+        <f t="array" ref="A66">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="4" t="e" cm="1" vm="8">
-        <f t="array" ref="A79">_xlfn._xlws.PY(7,0)</f>
+    <row r="78" spans="1:1" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A82" s="4" t="e" cm="1" vm="8">
+        <f t="array" ref="A82">_xlfn._xlws.PY(7,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A99" s="4" t="e" cm="1" vm="9">
-        <f t="array" ref="A99">_xlfn._xlws.PY(8,0)</f>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A102" s="4" t="e" cm="1" vm="9">
+        <f t="array" ref="A102">_xlfn._xlws.PY(8,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A117" s="4" t="e" cm="1" vm="10">
-        <f t="array" ref="A117">_xlfn._xlws.PY(9,0)</f>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A120" s="4" t="e" cm="1" vm="10">
+        <f t="array" ref="A120">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A131" s="4" t="e" cm="1" vm="11">
-        <f t="array" ref="A131">_xlfn._xlws.PY(10,0)</f>
+    <row r="132" spans="1:1" ht="147" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A134" s="4" t="e" cm="1" vm="11">
+        <f t="array" ref="A134">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A143" s="4" t="e" cm="1" vm="12">
-        <f t="array" ref="A143">_xlfn._xlws.PY(11,0)</f>
+    <row r="143" spans="1:1" ht="113.65" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A146" s="4" t="e" cm="1" vm="12">
+        <f t="array" ref="A146">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A155" s="4" t="e" cm="1" vm="13">
-        <f t="array" ref="A155">_xlfn._xlws.PY(12,0)</f>
+    <row r="155" spans="1:1" ht="167.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A158" s="4" t="e" cm="1" vm="13">
+        <f t="array" ref="A158">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A177" s="4" t="e" cm="1" vm="14">
-        <f t="array" ref="A177">_xlfn._xlws.PY(13,0)</f>
+    <row r="177" spans="1:1" ht="114.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A180" s="4" t="e" cm="1" vm="14">
+        <f t="array" ref="A180">_xlfn._xlws.PY(13,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A197" s="4" t="str" cm="1">
-        <f t="array" ref="A197:H204">_xlfn._xlws.PY(14,0)</f>
+    <row r="196" spans="1:8" ht="177.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A200" s="4" t="str" cm="1">
+        <f t="array" ref="A200:H207">_xlfn._xlws.PY(14,0)</f>
         <v/>
       </c>
-      <c r="B197" s="4" t="str">
+      <c r="B200" s="4" t="str">
         <v>mpg</v>
       </c>
-      <c r="C197" s="4" t="str">
+      <c r="C200" s="4" t="str">
         <v>cylinders</v>
       </c>
-      <c r="D197" s="4" t="str">
+      <c r="D200" s="4" t="str">
         <v>displacement</v>
       </c>
-      <c r="E197" s="4" t="str">
+      <c r="E200" s="4" t="str">
         <v>horsepower</v>
       </c>
-      <c r="F197" s="4" t="str">
+      <c r="F200" s="4" t="str">
         <v>weight</v>
       </c>
-      <c r="G197" s="4" t="str">
+      <c r="G200" s="4" t="str">
         <v>acceleration</v>
       </c>
-      <c r="H197" s="4" t="str">
+      <c r="H200" s="4" t="str">
         <v>model_year</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A198" s="4" t="str">
-        <v>mpg</v>
-      </c>
-      <c r="B198" s="4">
-        <v>1</v>
-      </c>
-      <c r="C198" s="4">
-        <v>-0.78627226915628468</v>
-      </c>
-      <c r="D198" s="4">
-        <v>-0.74790943103350538</v>
-      </c>
-      <c r="E198" s="4">
-        <v>-0.69064315601834925</v>
-      </c>
-      <c r="F198" s="4">
-        <v>-0.75528713492250599</v>
-      </c>
-      <c r="G198" s="4">
-        <v>0.55894731397140851</v>
-      </c>
-      <c r="H198" s="4">
-        <v>-1.8773081852925172E-2</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A199" s="4" t="str">
-        <v>cylinders</v>
-      </c>
-      <c r="B199" s="4">
-        <v>-0.78627226915628468</v>
-      </c>
-      <c r="C199" s="4">
-        <v>1</v>
-      </c>
-      <c r="D199" s="4">
-        <v>0.95090061798664194</v>
-      </c>
-      <c r="E199" s="4">
-        <v>0.90099373386577719</v>
-      </c>
-      <c r="F199" s="4">
-        <v>0.91267795874949453</v>
-      </c>
-      <c r="G199" s="4">
-        <v>-0.64366089242948299</v>
-      </c>
-      <c r="H199" s="4">
-        <v>-9.1942664715094335E-3</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A200" s="4" t="str">
-        <v>displacement</v>
-      </c>
-      <c r="B200" s="4">
-        <v>-0.74790943103350538</v>
-      </c>
-      <c r="C200" s="4">
-        <v>0.95090061798664194</v>
-      </c>
-      <c r="D200" s="4">
-        <v>1</v>
-      </c>
-      <c r="E200" s="4">
-        <v>0.89247642477052325</v>
-      </c>
-      <c r="F200" s="4">
-        <v>0.87199796965664167</v>
-      </c>
-      <c r="G200" s="4">
-        <v>-0.62323054423620383</v>
-      </c>
-      <c r="H200" s="4">
-        <v>2.2402916481058133E-2</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201" s="4" t="str">
-        <v>horsepower</v>
+        <v>mpg</v>
       </c>
       <c r="B201" s="4">
+        <v>1</v>
+      </c>
+      <c r="C201" s="4">
+        <v>-0.78627226915628468</v>
+      </c>
+      <c r="D201" s="4">
+        <v>-0.74790943103350538</v>
+      </c>
+      <c r="E201" s="4">
         <v>-0.69064315601834925</v>
       </c>
-      <c r="C201" s="4">
-        <v>0.90099373386577719</v>
-      </c>
-      <c r="D201" s="4">
-        <v>0.89247642477052325</v>
-      </c>
-      <c r="E201" s="4">
-        <v>1</v>
-      </c>
       <c r="F201" s="4">
-        <v>0.83464897621101919</v>
+        <v>-0.75528713492250599</v>
       </c>
       <c r="G201" s="4">
-        <v>-0.57729736467931814</v>
+        <v>0.55894731397140851</v>
       </c>
       <c r="H201" s="4">
-        <v>3.109573764826493E-2</v>
+        <v>-1.8773081852925172E-2</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A202" s="4" t="str">
-        <v>weight</v>
+        <v>cylinders</v>
       </c>
       <c r="B202" s="4">
-        <v>-0.75528713492250599</v>
+        <v>-0.78627226915628468</v>
       </c>
       <c r="C202" s="4">
+        <v>1</v>
+      </c>
+      <c r="D202" s="4">
+        <v>0.95090061798664194</v>
+      </c>
+      <c r="E202" s="4">
+        <v>0.90099373386577719</v>
+      </c>
+      <c r="F202" s="4">
         <v>0.91267795874949453</v>
       </c>
-      <c r="D202" s="4">
-        <v>0.87199796965664167</v>
-      </c>
-      <c r="E202" s="4">
-        <v>0.83464897621101919</v>
-      </c>
-      <c r="F202" s="4">
-        <v>1</v>
-      </c>
       <c r="G202" s="4">
-        <v>-0.61105286772043321</v>
+        <v>-0.64366089242948299</v>
       </c>
       <c r="H202" s="4">
-        <v>-1.0367952063320311E-2</v>
+        <v>-9.1942664715094335E-3</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A203" s="4" t="str">
-        <v>acceleration</v>
+        <v>displacement</v>
       </c>
       <c r="B203" s="4">
-        <v>0.55894731397140851</v>
+        <v>-0.74790943103350538</v>
       </c>
       <c r="C203" s="4">
-        <v>-0.64366089242948299</v>
+        <v>0.95090061798664194</v>
       </c>
       <c r="D203" s="4">
+        <v>1</v>
+      </c>
+      <c r="E203" s="4">
+        <v>0.89247642477052325</v>
+      </c>
+      <c r="F203" s="4">
+        <v>0.87199796965664167</v>
+      </c>
+      <c r="G203" s="4">
         <v>-0.62323054423620383</v>
       </c>
-      <c r="E203" s="4">
-        <v>-0.57729736467931814</v>
-      </c>
-      <c r="F203" s="4">
-        <v>-0.61105286772043321</v>
-      </c>
-      <c r="G203" s="4">
-        <v>1</v>
-      </c>
       <c r="H203" s="4">
-        <v>1.7399828573187046E-2</v>
+        <v>2.2402916481058133E-2</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204" s="4" t="str">
+        <v>horsepower</v>
+      </c>
+      <c r="B204" s="4">
+        <v>-0.69064315601834925</v>
+      </c>
+      <c r="C204" s="4">
+        <v>0.90099373386577719</v>
+      </c>
+      <c r="D204" s="4">
+        <v>0.89247642477052325</v>
+      </c>
+      <c r="E204" s="4">
+        <v>1</v>
+      </c>
+      <c r="F204" s="4">
+        <v>0.83464897621101919</v>
+      </c>
+      <c r="G204" s="4">
+        <v>-0.57729736467931814</v>
+      </c>
+      <c r="H204" s="4">
+        <v>3.109573764826493E-2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A205" s="4" t="str">
+        <v>weight</v>
+      </c>
+      <c r="B205" s="4">
+        <v>-0.75528713492250599</v>
+      </c>
+      <c r="C205" s="4">
+        <v>0.91267795874949453</v>
+      </c>
+      <c r="D205" s="4">
+        <v>0.87199796965664167</v>
+      </c>
+      <c r="E205" s="4">
+        <v>0.83464897621101919</v>
+      </c>
+      <c r="F205" s="4">
+        <v>1</v>
+      </c>
+      <c r="G205" s="4">
+        <v>-0.61105286772043321</v>
+      </c>
+      <c r="H205" s="4">
+        <v>-1.0367952063320311E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A206" s="4" t="str">
+        <v>acceleration</v>
+      </c>
+      <c r="B206" s="4">
+        <v>0.55894731397140851</v>
+      </c>
+      <c r="C206" s="4">
+        <v>-0.64366089242948299</v>
+      </c>
+      <c r="D206" s="4">
+        <v>-0.62323054423620383</v>
+      </c>
+      <c r="E206" s="4">
+        <v>-0.57729736467931814</v>
+      </c>
+      <c r="F206" s="4">
+        <v>-0.61105286772043321</v>
+      </c>
+      <c r="G206" s="4">
+        <v>1</v>
+      </c>
+      <c r="H206" s="4">
+        <v>1.7399828573187046E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A207" s="4" t="str">
         <v>model_year</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B207" s="4">
         <v>-1.8773081852925172E-2</v>
       </c>
-      <c r="C204" s="4">
+      <c r="C207" s="4">
         <v>-9.1942664715094335E-3</v>
       </c>
-      <c r="D204" s="4">
+      <c r="D207" s="4">
         <v>2.2402916481058133E-2</v>
       </c>
-      <c r="E204" s="4">
+      <c r="E207" s="4">
         <v>3.109573764826493E-2</v>
       </c>
-      <c r="F204" s="4">
+      <c r="F207" s="4">
         <v>-1.0367952063320311E-2</v>
       </c>
-      <c r="G204" s="4">
+      <c r="G207" s="4">
         <v>1.7399828573187046E-2</v>
       </c>
-      <c r="H204" s="4">
+      <c r="H207" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A207" s="4" t="e" cm="1" vm="15">
-        <f t="array" ref="A207">_xlfn._xlws.PY(15,0)</f>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A210" s="4" t="e" cm="1" vm="15">
+        <f t="array" ref="A210">_xlfn._xlws.PY(15,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A223" s="4" t="e" cm="1" vm="16">
-        <f t="array" ref="A223">_xlfn._xlws.PY(16,0)</f>
+    <row r="223" spans="1:1" ht="139.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A226" s="4" t="e" cm="1" vm="16">
+        <f t="array" ref="A226">_xlfn._xlws.PY(16,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A240" s="4" t="e" cm="1" vm="17">
-        <f t="array" ref="A240">_xlfn._xlws.PY(17,0)</f>
+    <row r="238" spans="1:1" ht="154.9" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A243" s="4" t="e" cm="1" vm="17">
+        <f t="array" ref="A243">_xlfn._xlws.PY(17,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A255" s="4" t="e" cm="1" vm="18">
-        <f t="array" ref="A255">_xlfn._xlws.PY(18,0)</f>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A258" s="4" t="e" cm="1" vm="18">
+        <f t="array" ref="A258">_xlfn._xlws.PY(18,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A270" s="4" t="e" cm="1" vm="19">
-        <f t="array" ref="A270">_xlfn._xlws.PY(19,0)</f>
+    <row r="269" spans="1:1" ht="116.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A273" s="4" t="e" cm="1" vm="19">
+        <f t="array" ref="A273">_xlfn._xlws.PY(19,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A290" s="4" t="e" cm="1" vm="20">
-        <f t="array" ref="A290">_xlfn._xlws.PY(20,0)</f>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A293" s="4" t="e" cm="1" vm="20">
+        <f t="array" ref="A293">_xlfn._xlws.PY(20,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A306" s="4" t="e" cm="1" vm="21">
-        <f t="array" ref="A306">_xlfn._xlws.PY(21,0)</f>
+    <row r="306" spans="1:1" ht="120.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A309" s="4" t="e" cm="1" vm="21">
+        <f t="array" ref="A309">_xlfn._xlws.PY(21,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A324" s="4" t="e" cm="1" vm="22">
-        <f t="array" ref="A324">_xlfn._xlws.PY(22,0)</f>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A327" s="4" t="e" cm="1" vm="22">
+        <f t="array" ref="A327">_xlfn._xlws.PY(22,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A343" s="4" t="e" cm="1" vm="23">
-        <f t="array" ref="A343">_xlfn._xlws.PY(23,0)</f>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A346" s="4" t="e" cm="1" vm="23">
+        <f t="array" ref="A346">_xlfn._xlws.PY(23,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
